--- a/www/download/IND.abstract_labour.emp.s.mv.rpO2.xlsx
+++ b/www/download/IND.abstract_labour.emp.s.mv.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25228.764</t>
+          <t>25228764105.8109</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25013.257</t>
+          <t>25013257331.9707</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27202.07</t>
+          <t>27202069971.7438</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>27107.276</t>
+          <t>27107276177.8856</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28613.742</t>
+          <t>28613742441.6492</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>28559.083</t>
+          <t>28559082996.2405</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32782.77</t>
+          <t>32782770377.6695</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29744.641</t>
+          <t>29744641493.5262</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>33414.499</t>
+          <t>33414499458.104</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>53251.863</t>
+          <t>53251863139.5549</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>39957.052</t>
+          <t>39957052233.6587</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>38587.039</t>
+          <t>38587038799.5065</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>34989.484</t>
+          <t>34989483508.0813</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>37986.429</t>
+          <t>37986429349.0818</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>40048.824</t>
+          <t>40048823859.9123</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13203.933</t>
+          <t>13203932694.0304</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13397.303</t>
+          <t>13397303311.4194</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13144.864</t>
+          <t>13144863983.6777</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13306.824</t>
+          <t>13306823760.418</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14392.5</t>
+          <t>14392500108.5286</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15330.935</t>
+          <t>15330934690.2407</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15550.406</t>
+          <t>15550405852.5676</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16249.35</t>
+          <t>16249350376.7173</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>16813.283</t>
+          <t>16813282938.2729</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17329.206</t>
+          <t>17329205617.8151</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16416.655</t>
+          <t>16416654530.4943</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>16130.845</t>
+          <t>16130845358.7006</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>16135.666</t>
+          <t>16135665701.315</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>16057.184</t>
+          <t>16057183880.4337</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>16949.964</t>
+          <t>16949964428.636</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24053.933</t>
+          <t>24053932591.0503</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24252.107</t>
+          <t>24252106530.245</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24838.577</t>
+          <t>24838577266.3648</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24745.895</t>
+          <t>24745895484.2415</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25590.42</t>
+          <t>25590419508.897</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>26080.124</t>
+          <t>26080124418.9822</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26201.39</t>
+          <t>26201390069.4022</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25925.427</t>
+          <t>25925426581.962</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>25723.401</t>
+          <t>25723401007.8499</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25881.4</t>
+          <t>25881399767.4076</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>26461.448</t>
+          <t>26461447892.4432</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>26996.562</t>
+          <t>26996561987.8049</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>27698.566</t>
+          <t>27698565713.8775</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>28284.533</t>
+          <t>28284533020.5126</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>27793.701</t>
+          <t>27793701018.4628</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11010.847</t>
+          <t>11010847461.4494</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11878.048</t>
+          <t>11878048460.4778</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12021.646</t>
+          <t>12021646108.2215</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10652.043</t>
+          <t>10652043493.3834</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10093.177</t>
+          <t>10093176586.6442</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9690.314</t>
+          <t>9690313835.36697</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11106.1</t>
+          <t>11106100049.3249</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10951.618</t>
+          <t>10951618479.7352</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10476.085</t>
+          <t>10476085169.2964</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>10478.813</t>
+          <t>10478813073.5066</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10155.572</t>
+          <t>10155572220.9562</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>9646.005</t>
+          <t>9646004821.16061</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10353.536</t>
+          <t>10353535762.4775</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>11631.22</t>
+          <t>11631220357.3114</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>11452.942</t>
+          <t>11452942465.7701</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>853209.365</t>
+          <t>853209365234.656</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>815283.598</t>
+          <t>815283597544.761</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>802646.558</t>
+          <t>802646557779.506</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>780752.41</t>
+          <t>780752410486.841</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>795232.859</t>
+          <t>795232858542.92</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>723069.666</t>
+          <t>723069666061.562</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>709128.762</t>
+          <t>709128762293.865</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>719912.128</t>
+          <t>719912128445.145</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>669780.085</t>
+          <t>669780084790.063</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>685120.52</t>
+          <t>685120519721.932</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>691635.763</t>
+          <t>691635763121.184</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>724794.479</t>
+          <t>724794478947.597</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>919802.423</t>
+          <t>919802422659.497</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>946099.788</t>
+          <t>946099787697.319</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>975784.098</t>
+          <t>975784098429.543</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>70349.29</t>
+          <t>70349289631.5116</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>69261.69</t>
+          <t>69261690327.3066</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>64371.669</t>
+          <t>64371668506.921</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65462.651</t>
+          <t>65462650510.5072</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>66671.519</t>
+          <t>66671519086.3172</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>63440.234</t>
+          <t>63440234088.9066</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>67293.723</t>
+          <t>67293723033.948</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>67324.528</t>
+          <t>67324528209.7216</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>67307.969</t>
+          <t>67307968526.831</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>70989.632</t>
+          <t>70989631806.2598</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>67357.301</t>
+          <t>67357300521.2193</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>72233.317</t>
+          <t>72233316550.3396</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>76331.941</t>
+          <t>76331940701.0673</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>79870.348</t>
+          <t>79870348001.8008</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>80278.476</t>
+          <t>80278476010.941</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8074453.846</t>
+          <t>8074453845892.98</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8096506.642</t>
+          <t>8096506642443.94</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7395455.147</t>
+          <t>7395455146961.52</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6886499.733</t>
+          <t>6886499732784.27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6121501.642</t>
+          <t>6121501642026.45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6281580</t>
+          <t>6281579999867.79</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7301525.237</t>
+          <t>7301525237449.27</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7870633.011</t>
+          <t>7870633011277.14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8733844.453</t>
+          <t>8733844452881.92</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9874101.662</t>
+          <t>9874101661938.32</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10446061.589</t>
+          <t>10446061588592.1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10212450.971</t>
+          <t>10212450970585.4</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>11007979.244</t>
+          <t>11007979244029.1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>11347615.295</t>
+          <t>11347615294582.8</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>11452802.016</t>
+          <t>11452802016115.8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1980.345</t>
+          <t>1980344571.82149</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1923.399</t>
+          <t>1923398562.27022</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1928.944</t>
+          <t>1928944376.45586</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1894.22</t>
+          <t>1894219858.90259</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1872.68</t>
+          <t>1872680380.08917</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1833.758</t>
+          <t>1833757842.76782</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1984.059</t>
+          <t>1984059438.68204</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2095.556</t>
+          <t>2095555802.84498</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2333.87</t>
+          <t>2333870192.36904</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2503.201</t>
+          <t>2503201309.849</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2638.159</t>
+          <t>2638158946.4199</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2912.941</t>
+          <t>2912941124.65103</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>3110.6</t>
+          <t>3110600208.42751</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3139.603</t>
+          <t>3139603010.53791</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3161.886</t>
+          <t>3161886354.44969</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15571.177</t>
+          <t>15571176659.15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15731.659</t>
+          <t>15731659236.6255</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15859.927</t>
+          <t>15859927038.1421</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16270.911</t>
+          <t>16270910871.2578</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>16283.69</t>
+          <t>16283689703.9838</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>16703.242</t>
+          <t>16703242454.3099</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15632.747</t>
+          <t>15632747274.8116</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15335.143</t>
+          <t>15335143499.8706</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>16025.032</t>
+          <t>16025031684.4355</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>15939.069</t>
+          <t>15939069127.876</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>16153.278</t>
+          <t>16153277605.3007</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>16624.24</t>
+          <t>16624239738.6153</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>17200.011</t>
+          <t>17200010965.4034</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>18819.417</t>
+          <t>18819417067.1586</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>18011.268</t>
+          <t>18011267636.9457</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>114717.628</t>
+          <t>114717628092.918</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>114884.768</t>
+          <t>114884768461.375</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>112392.589</t>
+          <t>112392588776.141</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>113754.154</t>
+          <t>113754154372.335</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>113050.201</t>
+          <t>113050200648.751</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>112463.681</t>
+          <t>112463680839.819</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>113114.725</t>
+          <t>113114725142.627</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>112804.812</t>
+          <t>112804811663.755</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>110891.485</t>
+          <t>110891484723.983</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>114836.04</t>
+          <t>114836040411.301</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>114310.542</t>
+          <t>114310541850.276</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>114720.859</t>
+          <t>114720859232.46</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>116923.745</t>
+          <t>116923744794.173</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>120962.027</t>
+          <t>120962026992.639</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>118741.405</t>
+          <t>118741405320.403</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6945.908</t>
+          <t>6945907849.19895</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7189.985</t>
+          <t>7189985205.83284</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7658.489</t>
+          <t>7658489156.46477</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8902.418</t>
+          <t>8902418330.17574</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>9399.884</t>
+          <t>9399884190.01538</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9693.198</t>
+          <t>9693197888.15294</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10265.758</t>
+          <t>10265757923.3013</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10500.327</t>
+          <t>10500326508.1024</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10538.639</t>
+          <t>10538638687.9248</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10495.809</t>
+          <t>10495809416.1009</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10884.063</t>
+          <t>10884062540.9651</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>11857.872</t>
+          <t>11857871800.0646</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>12455.471</t>
+          <t>12455470756.8141</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>12017.745</t>
+          <t>12017745376.5636</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>11651.185</t>
+          <t>11651184677.6492</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>59228.885</t>
+          <t>59228885446.6921</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>57742.22</t>
+          <t>57742219979.4287</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>56972.615</t>
+          <t>56972615492.3239</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>58935.04</t>
+          <t>58935040179.7129</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>60471.107</t>
+          <t>60471107430.2988</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>61825.355</t>
+          <t>61825354727.7294</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>63550.855</t>
+          <t>63550854544.4135</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>67136.486</t>
+          <t>67136486224.9531</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>71630.157</t>
+          <t>71630157103.6628</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>73674.369</t>
+          <t>73674368725.8771</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>75102.593</t>
+          <t>75102593190.7753</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>77036.12</t>
+          <t>77036120431.192</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>78443.214</t>
+          <t>78443214245.8065</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>80228.58</t>
+          <t>80228579574.1286</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>75198.593</t>
+          <t>75198593114.0936</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11651.217</t>
+          <t>11651217255.4111</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>11641.489</t>
+          <t>11641488922.4411</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20264.249</t>
+          <t>20264248960.4427</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21657.093</t>
+          <t>21657093030.9374</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2302.102</t>
+          <t>2302102106.21274</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2191.034</t>
+          <t>2191034213.33524</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3263.827</t>
+          <t>3263826698.66478</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2192.427</t>
+          <t>2192426565.07912</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2050.5</t>
+          <t>2050499646.83609</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2532.921</t>
+          <t>2532920801.31963</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3315.376</t>
+          <t>3315376131.33877</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2505.318</t>
+          <t>2505318359.83247</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2496.354</t>
+          <t>2496353563.05514</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2571.313</t>
+          <t>2571313187.06922</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1965.832</t>
+          <t>1965832135.00031</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8540.097</t>
+          <t>8540096575.62606</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8551.292</t>
+          <t>8551292471.47303</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8849.657</t>
+          <t>8849657220.04673</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>8952.459</t>
+          <t>8952458684.81588</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9077.055</t>
+          <t>9077054640.08081</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9152.522</t>
+          <t>9152521681.07885</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9043.089</t>
+          <t>9043088503.2984</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8754.223</t>
+          <t>8754222587.30093</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8337.198</t>
+          <t>8337197550.55252</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8458.636</t>
+          <t>8458635585.97688</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>8675.569</t>
+          <t>8675569208.61464</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8856.745</t>
+          <t>8856745043.82612</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>9002.835</t>
+          <t>9002834689.10847</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>10177.403</t>
+          <t>10177402959.571</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>8751.042</t>
+          <t>8751042384.62991</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>63590.553</t>
+          <t>63590552659.0975</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>63191.143</t>
+          <t>63191143207.1726</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>63452.705</t>
+          <t>63452705477.8684</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>68363.595</t>
+          <t>68363595054.9945</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>71419.887</t>
+          <t>71419886832.6439</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>71021.63</t>
+          <t>71021630145.9185</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>70486.64</t>
+          <t>70486640363.8822</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>68561.64</t>
+          <t>68561639875.5759</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>67726.936</t>
+          <t>67726936037.409</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>67163.628</t>
+          <t>67163627966.6657</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>67857.125</t>
+          <t>67857124947.3207</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>68425.485</t>
+          <t>68425484945.4562</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>68659.708</t>
+          <t>68659708048.9899</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>68141.786</t>
+          <t>68141786497.21</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>66729.632</t>
+          <t>66729632387.1648</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>67835.121</t>
+          <t>67835121094.0521</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>73430.455</t>
+          <t>73430455145.7867</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83380.578</t>
+          <t>83380577867.2349</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>85810.931</t>
+          <t>85810930678.9099</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>83853.456</t>
+          <t>83853456363.6448</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>83323.762</t>
+          <t>83323761982.2049</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>82630.329</t>
+          <t>82630329004.7063</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>85346.35</t>
+          <t>85346349962.0328</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>85659.532</t>
+          <t>85659532166.0389</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>89635.247</t>
+          <t>89635247358.8236</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>92467.375</t>
+          <t>92467375085.1059</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>90216.922</t>
+          <t>90216922178.8236</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>87333.659</t>
+          <t>87333659126.7767</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>81843.081</t>
+          <t>81843080561.9933</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>73538.77</t>
+          <t>73538769505.1922</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19249.3</t>
+          <t>19249300195.3405</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19195.649</t>
+          <t>19195649033.1931</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21571.866</t>
+          <t>21571865909.4994</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22280.595</t>
+          <t>22280595184.7125</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>22006.467</t>
+          <t>22006466877.0748</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>21326.158</t>
+          <t>21326157538.6384</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18800.316</t>
+          <t>18800316154.039</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18394.566</t>
+          <t>18394566339.0294</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18284.627</t>
+          <t>18284626521.2588</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>22102.24</t>
+          <t>22102240147.3722</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>17871.738</t>
+          <t>17871737568.5763</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>20414.936</t>
+          <t>20414935828.8096</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>20399.655</t>
+          <t>20399655390.477</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>21034.964</t>
+          <t>21034964050.4406</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>21758.846</t>
+          <t>21758846011.4198</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15048.948</t>
+          <t>15048948419.7806</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14728.762</t>
+          <t>14728762361.5486</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17149.012</t>
+          <t>17149012255.0942</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17834.369</t>
+          <t>17834369094.839</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16837.285</t>
+          <t>16837285334.1583</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19529.062</t>
+          <t>19529061513.243</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17295.191</t>
+          <t>17295191152.9626</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20627.269</t>
+          <t>20627268936.1754</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19165.068</t>
+          <t>19165067541.3295</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>19405.404</t>
+          <t>19405404070.0581</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>18829.629</t>
+          <t>18829628539.4177</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>20323.251</t>
+          <t>20323251067.7903</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>21255.427</t>
+          <t>21255427145.5245</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>18155.094</t>
+          <t>18155093836.3522</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>18578.032</t>
+          <t>18578031635.9342</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>681770.205</t>
+          <t>681770204678.37</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>737480.132</t>
+          <t>737480132187.301</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>706508.722</t>
+          <t>706508721501.547</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>733675.502</t>
+          <t>733675501863.233</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>568261.348</t>
+          <t>568261348298.242</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>536509.484</t>
+          <t>536509483561.938</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>465863.917</t>
+          <t>465863917382.884</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>484531.29</t>
+          <t>484531290196.748</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>518580.223</t>
+          <t>518580223015.55</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>541516.833</t>
+          <t>541516833183.985</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>456973.521</t>
+          <t>456973521171.526</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>366318.938</t>
+          <t>366318938385.59</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>385774.116</t>
+          <t>385774116176.142</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>366261.954</t>
+          <t>366261954129.045</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>360285.502</t>
+          <t>360285502159.096</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3860343.189</t>
+          <t>3860343188613.65</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3541282.312</t>
+          <t>3541282312135.32</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3285912.326</t>
+          <t>3285912326062.16</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2828153.561</t>
+          <t>2828153560847.95</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2594280.698</t>
+          <t>2594280698115.41</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3498625.883</t>
+          <t>3498625883038.18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4458494.327</t>
+          <t>4458494327471.98</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>5337661.731</t>
+          <t>5337661730525.42</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6367602.019</t>
+          <t>6367602018840.65</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7552708.669</t>
+          <t>7552708669127.4</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>8122248.025</t>
+          <t>8122248024562.67</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8266362.985</t>
+          <t>8266362985007.64</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>8392087.473</t>
+          <t>8392087473060.46</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>8819960.624</t>
+          <t>8819960623922.06</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>9276517.027</t>
+          <t>9276517027301.3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>12334.863</t>
+          <t>12334863121.1215</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12795.236</t>
+          <t>12795235570.7475</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7013.033</t>
+          <t>7013033256.7496</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>8230.038</t>
+          <t>8230038283.04573</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8790.291</t>
+          <t>8790291272.36153</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>10292.457</t>
+          <t>10292456684.3507</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10099.928</t>
+          <t>10099927528.6801</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9882.353</t>
+          <t>9882353038.26119</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>9497.515</t>
+          <t>9497515174.77036</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>8604.541</t>
+          <t>8604541125.88824</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>8451.789</t>
+          <t>8451788626.26855</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>8551.401</t>
+          <t>8551401251.13438</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>8916.133</t>
+          <t>8916133201.87906</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>23311.76</t>
+          <t>23311759887.6766</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>9796.151</t>
+          <t>9796151407.19007</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>136053.199</t>
+          <t>136053198505.595</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>146385.529</t>
+          <t>146385529240.363</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>145585.348</t>
+          <t>145585348366.279</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>146767.566</t>
+          <t>146767565976.523</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>148959.209</t>
+          <t>148959209296.126</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>157771.678</t>
+          <t>157771677671.959</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>153584.415</t>
+          <t>153584415332.99</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>160726.89</t>
+          <t>160726889787.5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>185177.482</t>
+          <t>185177482051.65</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>171959.554</t>
+          <t>171959554262.764</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>169776.806</t>
+          <t>169776806027.427</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>170440.042</t>
+          <t>170440041923.39</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>162793.023</t>
+          <t>162793023126.573</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>156641.991</t>
+          <t>156641990759.823</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>149365.772</t>
+          <t>149365772269.786</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>548128.831</t>
+          <t>548128831188.865</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>488821.561</t>
+          <t>488821560904.096</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>559050.262</t>
+          <t>559050261743.748</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>557070.215</t>
+          <t>557070215016.518</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>500693.06</t>
+          <t>500693060296.587</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>531848.927</t>
+          <t>531848927035.29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>540731.604</t>
+          <t>540731603533.315</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>483799.667</t>
+          <t>483799666765.61</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>468963.204</t>
+          <t>468963204349.761</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>467289.191</t>
+          <t>467289190912.696</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>469037.826</t>
+          <t>469037826073.906</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>471734.626</t>
+          <t>471734626404.743</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>477221.215</t>
+          <t>477221214558.228</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>464983.75</t>
+          <t>464983749716.84</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>428368.155</t>
+          <t>428368155414.985</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>133688.304</t>
+          <t>133688303875.715</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>144101.218</t>
+          <t>144101217755.923</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>147519.929</t>
+          <t>147519928672.572</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>144015.959</t>
+          <t>144015959309.841</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>119114.905</t>
+          <t>119114905254.229</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>120546.584</t>
+          <t>120546583521.256</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>123631.221</t>
+          <t>123631221381.364</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>139951.595</t>
+          <t>139951594585.819</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>141215.857</t>
+          <t>141215857213.373</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>155309.575</t>
+          <t>155309575064.091</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>159649.974</t>
+          <t>159649974290.855</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>165042.264</t>
+          <t>165042263641.178</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>163347.6</t>
+          <t>163347599946.019</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>161020.83</t>
+          <t>161020829607.827</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>163686.593</t>
+          <t>163686593229.766</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11725.807</t>
+          <t>11725807324.3833</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>17652.847</t>
+          <t>17652846705.0808</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4463.827</t>
+          <t>4463827357.34379</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>5089.718</t>
+          <t>5089718341.35536</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5181.632</t>
+          <t>5181632020.4177</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4642.332</t>
+          <t>4642332370.66657</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3878.963</t>
+          <t>3878962592.33332</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4252.086</t>
+          <t>4252086087.33428</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4599.648</t>
+          <t>4599648419.80958</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4103.146</t>
+          <t>4103145752.94072</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>4707.042</t>
+          <t>4707041867.71965</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5382.376</t>
+          <t>5382376267.62767</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>4956.038</t>
+          <t>4956038496.69774</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>4852.357</t>
+          <t>4852356778.05433</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4871.076</t>
+          <t>4871076073.69344</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1508.049</t>
+          <t>1508049006.44851</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>863.948</t>
+          <t>863948044.043033</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>793.68</t>
+          <t>793680329.017021</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>844.536</t>
+          <t>844535941.672901</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>901.69</t>
+          <t>901690359.314041</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>848.879</t>
+          <t>848878869.637316</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>799.44</t>
+          <t>799440136.028264</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>841.339</t>
+          <t>841338558.354347</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>860.009</t>
+          <t>860008994.730137</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>928.401</t>
+          <t>928400794.836488</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>925.623</t>
+          <t>925623438.810552</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>962.123</t>
+          <t>962123067.806969</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1004.447</t>
+          <t>1004447251.86635</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1096.382</t>
+          <t>1096382248.94273</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1077.533</t>
+          <t>1077533399.21994</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3461.766</t>
+          <t>3461765653.48091</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3552.794</t>
+          <t>3552794088.88874</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2989.758</t>
+          <t>2989758401.14727</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3215.22</t>
+          <t>3215219540.27468</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3436.731</t>
+          <t>3436731405.8975</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3339.765</t>
+          <t>3339764549.25106</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2881.9</t>
+          <t>2881899759.16443</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3333.578</t>
+          <t>3333577853.02922</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4721.157</t>
+          <t>4721157409.76869</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>14607.358</t>
+          <t>14607357783.5086</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>304417.368</t>
+          <t>304417368298.068</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>45528.022</t>
+          <t>45528022067.5268</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3296.911</t>
+          <t>3296910651.98687</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3245.16</t>
+          <t>3245159630.62705</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2798.944</t>
+          <t>2798943502.13098</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>311575.121</t>
+          <t>311575121055.043</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>313203.125</t>
+          <t>313203125117.288</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>316468.824</t>
+          <t>316468823835.525</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>327370.157</t>
+          <t>327370157148.911</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>339807.322</t>
+          <t>339807321797.186</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>360417.036</t>
+          <t>360417035671.689</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>378218.963</t>
+          <t>378218963023.409</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>393261.791</t>
+          <t>393261790716.43</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>399034.377</t>
+          <t>399034376625.884</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>403210.932</t>
+          <t>403210932051.775</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>404400.064</t>
+          <t>404400064185.578</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>435090.65</t>
+          <t>435090649952.038</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>443481.105</t>
+          <t>443481104784.898</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>476214.098</t>
+          <t>476214097771.678</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>462172.321</t>
+          <t>462172320791.925</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3022.881</t>
+          <t>3022881380.87258</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3013.689</t>
+          <t>3013689421.25384</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2972.711</t>
+          <t>2972711369.97767</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3000.594</t>
+          <t>3000594053.02064</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2957.128</t>
+          <t>2957128300.21702</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2773.597</t>
+          <t>2773597387.95884</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2394.049</t>
+          <t>2394048823.64792</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2788.483</t>
+          <t>2788483301.39827</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2768.691</t>
+          <t>2768691182.47097</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2871.148</t>
+          <t>2871148038.65578</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3912.492</t>
+          <t>3912491784.66955</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3203.459</t>
+          <t>3203458742.74327</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3474.834</t>
+          <t>3474834454.95969</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3358.98</t>
+          <t>3358980160.0876</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3581.774</t>
+          <t>3581773648.17589</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>24563.22</t>
+          <t>24563219501.7847</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>23679.112</t>
+          <t>23679112266.1543</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23222.021</t>
+          <t>23222020684.5477</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>23753.063</t>
+          <t>23753062965.5758</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23445.517</t>
+          <t>23445517336.0238</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>23188.572</t>
+          <t>23188571843.1596</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>22539.143</t>
+          <t>22539143133.0093</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>21321.532</t>
+          <t>21321532315.2746</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>20962.02</t>
+          <t>20962020120.569</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>20728.852</t>
+          <t>20728851653.9442</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>20563.458</t>
+          <t>20563457850.2007</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>20824.208</t>
+          <t>20824207567.0901</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>21452.286</t>
+          <t>21452286055.722</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>21669.143</t>
+          <t>21669143258.7379</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>20710.426</t>
+          <t>20710426203.2182</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>73775.521</t>
+          <t>73775520765.5835</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>69093.453</t>
+          <t>69093452777.9936</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>68917.451</t>
+          <t>68917451217.8186</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>72187.037</t>
+          <t>72187036573.9352</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>75131.983</t>
+          <t>75131982949.4079</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>60059.772</t>
+          <t>60059771923.158</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>65048.495</t>
+          <t>65048494959.3697</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>70421.554</t>
+          <t>70421553668.6893</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>69883.056</t>
+          <t>69883056149.4404</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>69002.96</t>
+          <t>69002959901.0656</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>78298.23</t>
+          <t>78298230299.0234</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>76565.642</t>
+          <t>76565642198.4974</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>73071.919</t>
+          <t>73071919193.3945</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>73202.873</t>
+          <t>73202873197.6875</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>74825.174</t>
+          <t>74825174404.4269</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>19404.232</t>
+          <t>19404231884.8224</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19275.931</t>
+          <t>19275930896.9223</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19420.891</t>
+          <t>19420891361.4591</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>19869.685</t>
+          <t>19869684504.5177</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20394.892</t>
+          <t>20394892096.2377</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>20848.83</t>
+          <t>20848829699.0542</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20478.294</t>
+          <t>20478293758.2701</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>20055.891</t>
+          <t>20055891179.1481</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19492.104</t>
+          <t>19492103923.7956</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>19686.938</t>
+          <t>19686938195.6793</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19684.538</t>
+          <t>19684537688.6731</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>18419.883</t>
+          <t>18419882845.2949</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>17728.771</t>
+          <t>17728770708.5269</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>17687.985</t>
+          <t>17687984788.8366</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>17283.242</t>
+          <t>17283241520.9419</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>102527.866</t>
+          <t>102527866032.971</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>89801.727</t>
+          <t>89801727353.5303</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>92417.633</t>
+          <t>92417632968.7296</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>90101.455</t>
+          <t>90101455399.1669</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>94309.759</t>
+          <t>94309758598.4576</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>92896.133</t>
+          <t>92896133182.0217</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>109195.126</t>
+          <t>109195126289.798</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>105470.033</t>
+          <t>105470033151.572</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>109669.585</t>
+          <t>109669585296.276</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>108355.488</t>
+          <t>108355488467.684</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>97762.548</t>
+          <t>97762548307.8168</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>105065.557</t>
+          <t>105065557466.543</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>32715.394</t>
+          <t>32715394280.5331</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>34019.225</t>
+          <t>34019224760.5491</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>36304.021</t>
+          <t>36304021498.6449</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>781964.089</t>
+          <t>781964089479.977</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>678598.809</t>
+          <t>678598809468.885</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>582835.305</t>
+          <t>582835304898.73</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>536098.43</t>
+          <t>536098429759.902</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>480852.945</t>
+          <t>480852945102.678</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>487575.57</t>
+          <t>487575569949.212</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>509937.083</t>
+          <t>509937082821.636</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>500514.153</t>
+          <t>500514153127.051</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>507267.897</t>
+          <t>507267897244.98</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>604623.803</t>
+          <t>604623802546.002</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>659708.079</t>
+          <t>659708078611.338</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>647831.098</t>
+          <t>647831097920.87</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>630350.015</t>
+          <t>630350015379.547</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>627445.823</t>
+          <t>627445823031.196</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>581372.323</t>
+          <t>581372322728.186</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5490.582</t>
+          <t>5490581687.42159</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5933.064</t>
+          <t>5933063724.78228</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5607.622</t>
+          <t>5607622030.082</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5115.001</t>
+          <t>5115001232.60991</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5371.085</t>
+          <t>5371084714.11946</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5144.488</t>
+          <t>5144488086.15751</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5325.183</t>
+          <t>5325182951.71842</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>5430.572</t>
+          <t>5430572495.86428</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>5169.329</t>
+          <t>5169329401.69948</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>5547.465</t>
+          <t>5547465085.71083</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>5918.266</t>
+          <t>5918266289.47426</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6128.89</t>
+          <t>6128890019.93407</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>6119.184</t>
+          <t>6119183563.65489</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>7274.683</t>
+          <t>7274682950.32894</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>7408.564</t>
+          <t>7408564483.74297</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2425.574</t>
+          <t>2425573905.8489</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2532.4</t>
+          <t>2532400168.60739</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2480.322</t>
+          <t>2480322159.87752</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2530.228</t>
+          <t>2530228106.25375</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2496.388</t>
+          <t>2496387721.26772</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2490.523</t>
+          <t>2490522737.23708</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2502.646</t>
+          <t>2502646368.04664</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2577.148</t>
+          <t>2577147830.61259</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2559.418</t>
+          <t>2559418248.38967</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2563.479</t>
+          <t>2563479397.41313</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2565.957</t>
+          <t>2565957134.78659</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2642.911</t>
+          <t>2642911200.73257</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2599.804</t>
+          <t>2599804367.44307</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2809.302</t>
+          <t>2809302401.68173</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2660.018</t>
+          <t>2660017670.4057</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9570.885</t>
+          <t>9570885152.2757</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9849.663</t>
+          <t>9849663323.61032</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9683.785</t>
+          <t>9683784563.11233</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>9952.624</t>
+          <t>9952623526.6265</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10405.951</t>
+          <t>10405951101.7526</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10925.685</t>
+          <t>10925685308.8274</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11103.763</t>
+          <t>11103763203.8534</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>11039.28</t>
+          <t>11039279586.4038</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>10807.731</t>
+          <t>10807730727.5431</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>10916.722</t>
+          <t>10916721518.0193</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10817.626</t>
+          <t>10817626230.5757</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>11568.332</t>
+          <t>11568332438.2261</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>11671.424</t>
+          <t>11671423986.3387</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>11327.789</t>
+          <t>11327789120.3176</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>10896.692</t>
+          <t>10896691842.5661</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>140735.588</t>
+          <t>140735587717.796</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>142136.262</t>
+          <t>142136262416.167</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>164100.131</t>
+          <t>164100130666.846</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>166349.066</t>
+          <t>166349066166.328</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>168626.468</t>
+          <t>168626468455.832</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>302894.343</t>
+          <t>302894343161.254</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>405930.532</t>
+          <t>405930532310.195</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>923090.657</t>
+          <t>923090657228.193</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1012777.643</t>
+          <t>1012777643224.26</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1025300.245</t>
+          <t>1025300244637.97</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1096225.309</t>
+          <t>1096225309102.42</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1111373.78</t>
+          <t>1111373779555.98</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1084477.951</t>
+          <t>1084477951398.73</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1143969.78</t>
+          <t>1143969779610.2</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1176227.923</t>
+          <t>1176227922559.28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>58629.273</t>
+          <t>58629272904.777</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>52681.359</t>
+          <t>52681358869.8139</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>53145.262</t>
+          <t>53145261920.7508</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>54003.95</t>
+          <t>54003950135.3717</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>53119.029</t>
+          <t>53119029096.9688</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>56684.849</t>
+          <t>56684848816.8793</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>57180.615</t>
+          <t>57180615498.0422</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>55275.572</t>
+          <t>55275572258.9736</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>56874.372</t>
+          <t>56874371564.9614</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>57881.071</t>
+          <t>57881070918.1474</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>60268.967</t>
+          <t>60268966902.6434</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>66843.468</t>
+          <t>66843468113.1289</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>72544.555</t>
+          <t>72544555266.916</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>77382.284</t>
+          <t>77382284259.8557</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>76745.657</t>
+          <t>76745656776.9835</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>506014.689</t>
+          <t>506014689195.751</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>541213.844</t>
+          <t>541213844138.5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>542755.039</t>
+          <t>542755038962.623</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>532171.896</t>
+          <t>532171895881.916</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>613934.186</t>
+          <t>613934185537.902</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>631893.533</t>
+          <t>631893532800.206</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>661712.588</t>
+          <t>661712587980.413</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>671763.044</t>
+          <t>671763044111.163</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>720994.476</t>
+          <t>720994476340.435</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>638250.46</t>
+          <t>638250460061.03</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>653559.182</t>
+          <t>653559182388.972</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>670195.094</t>
+          <t>670195093654.758</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>630993.681</t>
+          <t>630993681357.622</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>623485.691</t>
+          <t>623485691032.109</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>588779.409</t>
+          <t>588779408737.775</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>155827970.989</t>
+          <t>155827970988504</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>149445606.057</t>
+          <t>149445606057324</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>158517949.465</t>
+          <t>158517949465089</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>171182455.505</t>
+          <t>171182455505399</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>187786944.561</t>
+          <t>187786944560748</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>226028085.051</t>
+          <t>226028085050633</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>241892513.244</t>
+          <t>241892513244266</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>229693141.746</t>
+          <t>229693141745934</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>244493186.339</t>
+          <t>244493186338795</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>236882589.93</t>
+          <t>236882589930044</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>243764049.81</t>
+          <t>243764049810257</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>239527272.088</t>
+          <t>239527272087600</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>210680458.643</t>
+          <t>210680458642506</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>192774429.465</t>
+          <t>192774429464613</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>176069625.387</t>
+          <t>176069625386819</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>172712553.878</t>
+          <t>172712553877567</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>165933357.542</t>
+          <t>165933357542436</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>174010974.511</t>
+          <t>174010974510528</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>185685203.624</t>
+          <t>185685203624013</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>201096086.453</t>
+          <t>201096086452683</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>240507117.725</t>
+          <t>240507117725289</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>258473701.366</t>
+          <t>258473701365833</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>248253621.487</t>
+          <t>248253621487131</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>265102666.971</t>
+          <t>265102666970944</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>259932456.421</t>
+          <t>259932456420511</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>268300073.326</t>
+          <t>268300073326117</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>263738081.744</t>
+          <t>263738081744095</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>235841108.061</t>
+          <t>235841108060784</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>218800287.738</t>
+          <t>218800287737640</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>202548556.198</t>
+          <t>202548556197934</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>abstract_labour.emp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
